--- a/artfynd/A 51807-2025 artfynd.xlsx
+++ b/artfynd/A 51807-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115629185</v>
       </c>
       <c r="B2" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,7 +769,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+          <t>Sandra Johansson, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
